--- a/#Uad50#Ud68c#Uc77c#Uc815.xlsx
+++ b/#Uad50#Ud68c#Uc77c#Uc815.xlsx
@@ -5,11 +5,11 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\군포은혜영문\Web\Gunpo_Eunhye_Corps_Family_Management_System_v6.2_엑셀공지_교회일정\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\군포은혜영문\Web\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939900" windowHeight="17090" tabRatio="500"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25340" windowHeight="11490" tabRatio="500"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="교회일정" sheetId="1" r:id="rId4"/>
@@ -22,58 +22,34 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <x:si>
-    <x:t>회의</x:t>
+    <x:t>운영위원회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각 그룹별</x:t>
   </x:si>
   <x:si>
     <x:t>항목</x:t>
   </x:si>
   <x:si>
-    <x:t>장소</x:t>
+    <x:t>회의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주의</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7월 운영위원회의</x:t>
   </x:si>
   <x:si>
     <x:t>모임</x:t>
   </x:si>
   <x:si>
-    <x:t>행사명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>날짜</x:t>
-  </x:si>
-  <x:si>
-    <x:t>담당</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그룹장</x:t>
-  </x:si>
-  <x:si>
     <x:t>열 이름과 순서를 변경하지 마세요.</x:t>
   </x:si>
   <x:si>
-    <x:t>본당, 교육관, 외부 장소 등</x:t>
+    <x:t>예배/기도회/회의/행사/교육/전도/봉사/친교/기타 중 선택</x:t>
   </x:si>
   <x:si>
-    <x:t>준비물, 종료일, 세부 안내 등</x:t>
-  </x:si>
-  <x:si>
-    <x:t>군포은혜영문 통합3주년 총동원 주일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7월 운영위원회의</x:t>
-  </x:si>
-  <x:si>
-    <x:t>교회일정 표준양식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24시간 형식 권장. 예: 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행사 날짜. yyyy-mm-dd 형식</x:t>
+    <x:t>작성 방법</x:t>
   </x:si>
   <x:si>
     <x:t>비고</x:t>
@@ -85,22 +61,40 @@
     <x:t>구분</x:t>
   </x:si>
   <x:si>
-    <x:t>복지관 3층</x:t>
+    <x:t>군포은혜영문 통합3주년 총동원 주일</x:t>
   </x:si>
   <x:si>
-    <x:t>각 그룹별</x:t>
+    <x:t>준비물, 종료일, 세부 안내 등</x:t>
   </x:si>
   <x:si>
-    <x:t>작성 방법</x:t>
+    <x:t>본당, 교육관, 외부 장소 등</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복지관 3층</x:t>
   </x:si>
   <x:si>
     <x:t>소그룹 모임</x:t>
   </x:si>
   <x:si>
-    <x:t>운영위원회</x:t>
+    <x:t>앱에 표시될 일정 제목</x:t>
   </x:si>
   <x:si>
-    <x:t>예배/기도회/회의/행사/교육/전도/봉사/친교/기타 중 선택</x:t>
+    <x:t>담당 부서·소그룹·담당자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행사명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>날짜</x:t>
+  </x:si>
+  <x:si>
+    <x:t>담당</x:t>
   </x:si>
   <x:si>
     <x:t>군포은혜영문</x:t>
@@ -109,19 +103,24 @@
     <x:t>날짜순으로 자동 정렬해 사용할 수 있습니다. 행사명·장소·담당을 빠짐없이 입력해 주세요.</x:t>
   </x:si>
   <x:si>
-    <x:t>담당 부서·소그룹·담당자</x:t>
+    <x:t>행사 날짜. yyyy-mm-dd 형식</x:t>
   </x:si>
   <x:si>
-    <x:t>앱에 표시될 일정 제목</x:t>
+    <x:t>24시간 형식 권장. 예: 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교회일정 표준양식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그룹장</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <x:numFmt numFmtId="165" formatCode="[$-412]AM/PM\ h:mm;@"/>
   </x:numFmts>
   <x:fonts count="9">
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -368,7 +367,7 @@
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="27">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
@@ -486,6 +485,35 @@
     </x:xf>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
+          <x:alignment horizontal="center" vertical="center"/>
+          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
+        </x:xf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+          <x:alignment horizontal="center" vertical="center"/>
+        </x:xf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
           <x:alignment horizontal="center" vertical="center"/>
           <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
@@ -506,35 +534,6 @@
       </mc:Choice>
       <mc:Fallback>
         <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-          <x:alignment horizontal="center" vertical="center"/>
-        </x:xf>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" hs:applyExtension="1">
-          <x:alignment horizontal="center" vertical="center"/>
-          <hs:parashape hs:lineSpacingType="betweenLines" hs:lineSpacing="75" hs:breakNonLatinWord="breakWord" hs:breakLatinWord="keepWord" hs:condense="0" hs:textAlignment="baseLine"/>
-        </x:xf>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
           <x:alignment horizontal="center" vertical="center"/>
         </x:xf>
       </mc:Fallback>
@@ -1119,7 +1118,7 @@
   <x:sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="13.550000000000001"/>
   <x:cols>
     <x:col min="1" max="1" width="17.7265625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="14.18359375" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="10" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="12" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="42.81640625" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="24" style="1" customWidth="1"/>
@@ -1128,110 +1127,110 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7" ht="32" customHeight="1">
-      <x:c r="A1" s="24" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B1" s="24"/>
-      <x:c r="C1" s="24"/>
-      <x:c r="D1" s="24"/>
-      <x:c r="E1" s="24"/>
-      <x:c r="F1" s="24"/>
-      <x:c r="G1" s="24"/>
+      <x:c r="A1" s="22" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B1" s="22"/>
+      <x:c r="C1" s="22"/>
+      <x:c r="D1" s="22"/>
+      <x:c r="E1" s="22"/>
+      <x:c r="F1" s="22"/>
+      <x:c r="G1" s="22"/>
     </x:row>
     <x:row r="2" spans="1:7" ht="28" customHeight="1">
-      <x:c r="A2" s="25" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B2" s="25"/>
-      <x:c r="C2" s="25"/>
-      <x:c r="D2" s="25"/>
-      <x:c r="E2" s="25"/>
-      <x:c r="F2" s="25"/>
-      <x:c r="G2" s="25"/>
+      <x:c r="A2" s="23" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B2" s="23"/>
+      <x:c r="C2" s="23"/>
+      <x:c r="D2" s="23"/>
+      <x:c r="E2" s="23"/>
+      <x:c r="F2" s="23"/>
+      <x:c r="G2" s="23"/>
     </x:row>
     <x:row r="4" spans="1:7" ht="24" customHeight="1">
       <x:c r="A4" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E4" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E4" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G4" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
-      <x:c r="A5" s="23">
+      <x:c r="A5" s="26">
         <x:v>46222</x:v>
       </x:c>
-      <x:c r="B5" s="26">
+      <x:c r="B5" s="24">
         <x:v>0.45833333333333331</x:v>
       </x:c>
-      <x:c r="C5" s="22" t="s">
-        <x:v>19</x:v>
+      <x:c r="C5" s="25" t="s">
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E5" s="22" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F5" s="22" t="s">
+      <x:c r="E5" s="25" t="s">
         <x:v>25</x:v>
       </x:c>
+      <x:c r="F5" s="25" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="G5" s="10"/>
     </x:row>
     <x:row r="6" spans="1:7">
-      <x:c r="A6" s="23">
+      <x:c r="A6" s="26">
         <x:v>46222</x:v>
       </x:c>
-      <x:c r="B6" s="26">
+      <x:c r="B6" s="24">
         <x:v>0.5625</x:v>
       </x:c>
-      <x:c r="C6" s="22" t="s">
+      <x:c r="C6" s="25" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D6" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E6" s="25" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="25" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G6" s="11"/>
+    </x:row>
+    <x:row r="7" spans="1:7">
+      <x:c r="A7" s="26">
+        <x:v>46229</x:v>
+      </x:c>
+      <x:c r="B7" s="24">
+        <x:v>0.625</x:v>
+      </x:c>
+      <x:c r="C7" s="25" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D6" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E6" s="22" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F6" s="22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G6" s="11"/>
-    </x:row>
-    <x:row r="7" spans="1:7">
-      <x:c r="A7" s="23">
-        <x:v>46229</x:v>
-      </x:c>
-      <x:c r="B7" s="26">
-        <x:v>0.625</x:v>
-      </x:c>
-      <x:c r="C7" s="22" t="s">
+      <x:c r="D7" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E7" s="25" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="25" t="s">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="7" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E7" s="22" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F7" s="22" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="G7" s="11"/>
     </x:row>
@@ -3010,7 +3009,7 @@
       <x:formula1>"예배,기도회,회의,행사,교육,전도,봉사,친교,기타"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -3019,7 +3018,7 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet2"/>
   <x:dimension ref="A1:B9"/>
-  <x:sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="13.550000000000001"/>
+  <x:sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="16" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="60" style="1" customWidth="1"/>
@@ -3027,78 +3026,78 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="16" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="17" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="18" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B2" s="20" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="18" t="s">
-        <x:v>5</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B3" s="20" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="18" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="20" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="18" t="s">
-        <x:v>4</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="20" t="s">
-        <x:v>30</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="18" t="s">
-        <x:v>2</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="20" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="18" t="s">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="20" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="18" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B8" s="20" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="19" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="21" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>